--- a/data/trans_camb/P16A09-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A09-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,46</t>
+          <t>-2,73; 0,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; -0,15</t>
+          <t>-3,36; -0,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,17</t>
+          <t>-2,11; 1,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,77</t>
+          <t>-0,53; 3,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,35</t>
+          <t>-2,01; 2,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,54</t>
+          <t>0,6; 4,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,56</t>
+          <t>-1,18; 1,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,49</t>
+          <t>-2,05; 0,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,3</t>
+          <t>-0,24; 2,24</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-70,95; 27,81</t>
+          <t>-70,67; 23,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-81,86; -0,84</t>
+          <t>-82,2; -3,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-57,5; 61,3</t>
+          <t>-55,38; 65,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 126,66</t>
+          <t>-16,29; 149,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,89; 85,26</t>
+          <t>-42,32; 82,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 166,63</t>
+          <t>10,51; 178,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,63; 57,87</t>
+          <t>-30,54; 53,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,6; 19,23</t>
+          <t>-50,25; 19,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 86,3</t>
+          <t>-6,02; 86,23</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,11</t>
+          <t>-1,72; 1,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,21</t>
+          <t>-2,56; 0,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -0,01</t>
+          <t>-2,83; -0,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,72</t>
+          <t>-0,26; 3,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,07</t>
+          <t>-2,55; 1,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,7</t>
+          <t>-1,84; 1,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,01</t>
+          <t>-0,49; 1,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,07</t>
+          <t>-2,08; 0,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,22</t>
+          <t>-2,18; 0,23</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,93; 61,34</t>
+          <t>-51,18; 54,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,76; 15,47</t>
+          <t>-72,25; 8,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,98; -1,12</t>
+          <t>-80,03; -0,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 102,91</t>
+          <t>-5,14; 111,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,64; 30,14</t>
+          <t>-44,92; 32,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 48,77</t>
+          <t>-31,35; 47,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 65,26</t>
+          <t>-12,3; 61,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,92; 2,1</t>
+          <t>-49,84; 5,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-51,79; 5,86</t>
+          <t>-49,2; 7,03</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,0</t>
+          <t>-2,22; 1,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,64</t>
+          <t>-2,31; 0,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,47</t>
+          <t>-2,44; 0,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 1,21</t>
+          <t>-3,65; 0,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,06</t>
+          <t>-4,67; -0,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; -1,06</t>
+          <t>-5,66; -0,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,5</t>
+          <t>-2,39; 0,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; -0,13</t>
+          <t>-2,92; -0,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,32; -0,62</t>
+          <t>-3,31; -0,51</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,98; 61,66</t>
+          <t>-68,65; 77,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,98; 44,53</t>
+          <t>-67,99; 49,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,52; 35,67</t>
+          <t>-67,75; 45,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 27,09</t>
+          <t>-48,9; 21,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,18; 3,72</t>
+          <t>-61,44; 1,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,48; -23,28</t>
+          <t>-75,51; -16,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 15,72</t>
+          <t>-48,06; 12,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,41; -2,63</t>
+          <t>-57,27; -0,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,45; -17,48</t>
+          <t>-64,7; -14,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,21</t>
+          <t>-2,86; 0,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; -1,32</t>
+          <t>-3,91; -1,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,98; -0,33</t>
+          <t>-3,05; -0,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,84</t>
+          <t>-1,45; 2,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,89; -0,01</t>
+          <t>-3,95; 0,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,01</t>
+          <t>-1,44; 3,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,05</t>
+          <t>-1,57; 1,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; -1,16</t>
+          <t>-3,42; -1,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,13</t>
+          <t>-1,65; 1,05</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,29; 8,11</t>
+          <t>-65,71; 14,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-89,26; -45,63</t>
+          <t>-89,6; -46,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,51; -10,07</t>
+          <t>-69,53; -6,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 61,13</t>
+          <t>-21,54; 61,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 2,13</t>
+          <t>-58,26; 1,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 64,11</t>
+          <t>-21,91; 66,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 25,86</t>
+          <t>-29,32; 32,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,8; -28,24</t>
+          <t>-66,77; -27,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 31,85</t>
+          <t>-31,83; 27,78</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,71; -0,03</t>
+          <t>-1,57; -0,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -0,88</t>
+          <t>-2,28; -0,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,95; -0,39</t>
+          <t>-1,91; -0,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,89</t>
+          <t>-0,29; 1,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,31; -0,32</t>
+          <t>-2,3; -0,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,02</t>
+          <t>-1,17; 1,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,67</t>
+          <t>-0,75; 0,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,98; -0,79</t>
+          <t>-2,07; -0,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,1</t>
+          <t>-1,22; 0,17</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,99; -0,8</t>
+          <t>-47,73; -3,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-68,52; -34,48</t>
+          <t>-69,12; -35,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,79; -15,98</t>
+          <t>-57,57; -16,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 42,16</t>
+          <t>-5,0; 44,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,08; -6,12</t>
+          <t>-41,15; -6,34</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 22,36</t>
+          <t>-20,76; 26,18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 18,43</t>
+          <t>-17,57; 17,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-46,32; -21,57</t>
+          <t>-47,11; -20,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,35; 2,89</t>
+          <t>-28,53; 4,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A09-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A09-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,51</t>
+          <t>-0,52</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,15</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 0,36</t>
+          <t>-2,84; 0,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,25</t>
+          <t>-3,21; -0,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,3</t>
+          <t>-2,23; 1,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 3,88</t>
+          <t>-0,76; 3,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,25</t>
+          <t>-1,78; 2,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,6</t>
+          <t>0,75; 4,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,52</t>
+          <t>-1,13; 1,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,52</t>
+          <t>-1,85; 0,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,24</t>
+          <t>-0,06; 2,65</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-17,46%</t>
+          <t>-17,62%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-70,67; 23,43</t>
+          <t>-73,03; 16,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-82,2; -3,92</t>
+          <t>-83,56; -7,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,38; 65,02</t>
+          <t>-59,89; 47,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 149,34</t>
+          <t>-18,46; 130,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,32; 82,84</t>
+          <t>-39,22; 83,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,51; 178,64</t>
+          <t>14,17; 174,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,54; 53,88</t>
+          <t>-28,44; 58,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 19,6</t>
+          <t>-46,88; 24,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 86,23</t>
+          <t>-1,89; 104,44</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,3</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,42</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,03</t>
+          <t>-1,82; 1,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,08</t>
+          <t>-2,68; -0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; -0,01</t>
+          <t>-2,36; 0,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,84</t>
+          <t>-0,29; 3,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,13</t>
+          <t>-2,72; 1,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,72</t>
+          <t>-1,68; 1,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,92</t>
+          <t>-0,5; 2,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,16</t>
+          <t>-2,14; 0,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,23</t>
+          <t>-1,44; 0,68</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-48,3%</t>
+          <t>-36,53%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-21,79%</t>
+          <t>-11,32%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,18; 54,94</t>
+          <t>-49,41; 54,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-72,25; 8,7</t>
+          <t>-71,44; 6,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,03; -0,03</t>
+          <t>-64,52; 18,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 111,94</t>
+          <t>-6,37; 105,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 32,81</t>
+          <t>-49,32; 31,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,35; 47,11</t>
+          <t>-28,11; 54,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 61,65</t>
+          <t>-11,76; 64,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,84; 5,29</t>
+          <t>-48,83; 5,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 7,03</t>
+          <t>-32,58; 25,29</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,99</t>
+          <t>-2,02</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-1,49</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,08</t>
+          <t>-2,35; 0,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,73</t>
+          <t>-2,35; 0,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,66</t>
+          <t>-2,56; 0,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 0,94</t>
+          <t>-3,74; 0,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; -0,03</t>
+          <t>-4,59; 0,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -0,77</t>
+          <t>-4,25; 0,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,45</t>
+          <t>-2,36; 0,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; -0,01</t>
+          <t>-2,88; -0,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; -0,51</t>
+          <t>-2,73; -0,1</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-34,33%</t>
+          <t>-37,67%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-49,2%</t>
+          <t>-33,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-42,61%</t>
+          <t>-34,54%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,65; 77,15</t>
+          <t>-66,27; 71,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,99; 49,97</t>
+          <t>-68,76; 45,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,75; 45,33</t>
+          <t>-71,54; 40,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,9; 21,51</t>
+          <t>-50,09; 20,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,44; 1,91</t>
+          <t>-61,33; 4,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-75,51; -16,61</t>
+          <t>-56,75; -0,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,06; 12,2</t>
+          <t>-47,62; 12,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,27; -0,21</t>
+          <t>-57,28; -2,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,7; -14,71</t>
+          <t>-52,93; -1,88</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,56</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,29</t>
+          <t>-2,64; 0,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; -1,39</t>
+          <t>-3,89; -1,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; -0,27</t>
+          <t>-2,95; -0,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,8</t>
+          <t>-1,42; 2,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,02</t>
+          <t>-3,95; -0,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,0</t>
+          <t>-1,26; 2,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,23</t>
+          <t>-1,6; 1,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; -1,04</t>
+          <t>-3,54; -1,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,05</t>
+          <t>-1,45; 0,9</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-45,96%</t>
+          <t>-44,59%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-6,31%</t>
+          <t>-6,02%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-65,71; 14,27</t>
+          <t>-62,8; 15,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-89,6; -46,63</t>
+          <t>-88,63; -42,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,53; -6,48</t>
+          <t>-66,35; -4,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 61,01</t>
+          <t>-22,2; 59,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,26; 1,04</t>
+          <t>-59,86; -2,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,91; 66,3</t>
+          <t>-17,42; 55,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,32; 32,36</t>
+          <t>-29,92; 32,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,77; -27,42</t>
+          <t>-65,63; -26,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-31,83; 27,78</t>
+          <t>-27,64; 23,13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,16</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,3</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; -0,11</t>
+          <t>-1,59; 0,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; -0,92</t>
+          <t>-2,31; -0,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; -0,43</t>
+          <t>-1,82; -0,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,9</t>
+          <t>-0,34; 1,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; -0,3</t>
+          <t>-2,29; -0,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,2</t>
+          <t>-0,55; 1,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,64</t>
+          <t>-0,72; 0,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,07; -0,76</t>
+          <t>-2,02; -0,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,17</t>
+          <t>-0,95; 0,28</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-39,75%</t>
+          <t>-35,94%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-13,43%</t>
+          <t>-7,43%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,73; -3,3</t>
+          <t>-47,8; 1,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-69,12; -35,13</t>
+          <t>-68,14; -33,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,57; -16,46</t>
+          <t>-54,17; -12,55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 44,72</t>
+          <t>-6,1; 42,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,15; -6,34</t>
+          <t>-41,89; -6,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 26,18</t>
+          <t>-9,38; 30,58</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 17,09</t>
+          <t>-16,41; 16,59</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-47,11; -20,6</t>
+          <t>-46,62; -22,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 4,57</t>
+          <t>-21,57; 8,15</t>
         </is>
       </c>
     </row>
